--- a/data/trans_orig/IP16A12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Provincia-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>42328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>52298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62867</t>
+          <t>62661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>44666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93568</t>
+          <t>93470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106726</t>
+          <t>107016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48046</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61500</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>46478</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>144008</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164667</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135576</t>
+          <t>136231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>155238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>315623</t>
+          <t>316939</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6296</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6489</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7384</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16862</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12977</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18793</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28480</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23895</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19566</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16964</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20800</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>81,56%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19403</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14938</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21447</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>66,92%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47883</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42328</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50929</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8789</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4897</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11445</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37551</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33879</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40053</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>58846</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52298</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62661</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36793</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44666</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>100689</t>
+          <t>72404</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>66955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107016</t>
+          <t>76023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15538</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12648</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17094</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16181</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13601</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17790</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>33192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2748</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8292</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9773</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6027</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12105</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>78,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7832</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6680</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4528</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8229</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>51,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3548</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7264</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7890</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10025</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>68,98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7662</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9277</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6343</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>11461</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>33,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>10255</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14937</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33530</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27927</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>37883</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>66,44%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>19531</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>14849</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23728</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>49,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>79,66%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>53758</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61691</t>
+          <t>60135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7720</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>55,22%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>33552</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>25608</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>42931</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>15258</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>131927</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>122548</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>139871</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>143728</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>164094</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136231</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155238</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>299657</t>
+          <t>252610</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>240630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>262864</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
